--- a/测试1.xlsx
+++ b/测试1.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00ED1D25"/>
     </font>
     <font>
       <color rgb="0023B14D"/>
@@ -58,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -70,6 +73,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -464,7 +470,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
@@ -476,17 +482,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>对话_使用参数化判断echo为true/false时返回的信息正确</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+          <t>对话_使用参数化判断echo为False时返回的信息正确</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -495,10 +501,10 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>对话_使用参数化判断echo为true/false时返回的信息正确</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+          <t>对话_使用参数化判断echo为True时返回的信息正确</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -512,7 +518,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
@@ -524,7 +530,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
@@ -534,7 +540,7 @@
           <t>对话_判断role为user、developer...等允许的角色时，返回结果正确</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -546,9 +552,9 @@
           <t>对话_判断role为自定义角色时，返回结果错误</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>passed</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -558,7 +564,7 @@
           <t>对话_判断stream为false时，传入stream_options，服务报400，提示信息正确</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -567,10 +573,10 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>对话_判断stream为true时，stream_options两个选项全为true时，所有chunk的usage不为None</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+          <t>对话_判断stream为false时，返回为ChatCompletion类型</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -579,10 +585,10 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>对话_判断stream为true时，返回为流式Stream类型</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+          <t>对话_判断stream为false时，返回为ChatCompletion类型</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -591,10 +597,10 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>对话_判断stream为true，continuous_usage_stats为true时，所有的usage不为None</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+          <t>对话_判断stream为true时，stream_options两个选项全为true时，所有chunk的usage不为None</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -603,10 +609,10 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>对话_判断stream为true，include_usage为true时，最后的usage不为None</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+          <t>对话_判断stream为true时，返回为流式AsyncStream类型</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -615,10 +621,10 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>对话_判断设置max_completion_tokens != max_tokens时，400报错，返回正确提示信息</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+          <t>对话_判断stream为true，continuous_usage_stats为true时，所有的usage不为None</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -627,10 +633,10 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>对话_判断设置max_completion_tokens == max_tokens时，返回正确信息</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+          <t>对话_判断stream为true，include_usage为true时，最后的usage不为None</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -639,10 +645,10 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>对话_判断设置max_completion_tokens时，输出文本最长为max_completion_tokens，stop reason为length</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+          <t>对话_判断简单的对话结果返回内容类型为str</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -651,10 +657,10 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>对话_判断设置max_tokens时，输出文本最长为max_tokens，stop reason为length</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+          <t>对话_判断设置max_completion_tokens != max_tokens时，400报错，返回正确提示信息</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -663,10 +669,10 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>对话_判断设置stop字符时，输出遇到stop字符停止输出</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+          <t>对话_判断设置max_completion_tokens == max_tokens时，返回正确信息</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -675,10 +681,10 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>对话_判断调用tool返回结果正确，同时验证role为tool时正确处理</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+          <t>对话_判断设置max_completion_tokens时，输出文本最长为max_completion_tokens，stop reason为length</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -687,10 +693,10 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>对话_设置max_completion_tokens时，使用束搜索</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+          <t>对话_判断设置max_tokens时，输出文本最长为max_tokens，stop reason为length</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -699,10 +705,10 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>对话_设置max_completion_tokens时，使用束搜索</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+          <t>对话_判断设置stop字符时，输出遇到stop字符停止输出</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -711,70 +717,70 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>文本补全_prompt为文本数组和token ids数组时batch_completions返回结果正确</t>
+          <t>对话_判断调用tool返回结果正确，同时验证role为tool时正确处理</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>文本补全_不设置max_tokens，使用束搜索</t>
+          <t>对话_设置max_completion_tokens时，使用束搜索</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断guided_decoding_type错误</t>
+          <t>对话_设置max_completion_tokens时，使用束搜索</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断n=3时，parallel_streaming回结果正确</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>passed</t>
+          <t>文本补全_prompt为文本数组和token ids数组时batch_completions返回结果正确</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断prompt为token ids，返回结果正确</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>passed</t>
+          <t>文本补全_不设置max_tokens，使用束搜索</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断stream模式下，continuous_usage_stats为true时返回结果正确</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+          <t>文本补全_判断guided_decoding_type错误</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -783,22 +789,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断stream模式下，include_usage为true时返回结果正确</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>passed</t>
+          <t>文本补全_判断n=3时，parallel_streaming回结果正确</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断stream模式下，stream options全为false时返回结果正确</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+          <t>文本补全_判断prompt为token ids，返回结果正确</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -807,10 +813,10 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断stream模式下，stream_options全为true时返回结果正确</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+          <t>文本补全_判断stream模式下，continuous_usage_stats为true时返回结果正确</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -819,10 +825,10 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断stream模式返回结果正确</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+          <t>文本补全_判断stream模式下，include_usage为true时返回结果正确</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -831,10 +837,10 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断使用guided_grammar时返回文本格式正确</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+          <t>文本补全_判断stream模式下，stream options全为false时返回结果正确</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -843,10 +849,10 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断使用guided_json时返回文本格式正确</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+          <t>文本补全_判断stream模式下，stream_options全为true时返回结果正确</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -855,10 +861,10 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断温度不同返回结果改变</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+          <t>文本补全_判断stream模式返回结果正确</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -867,46 +873,46 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断目前不支持guided_choice</t>
+          <t>文本补全_判断使用guided_grammar时返回文本格式正确</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>broken</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断目前不支持guided_regex</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>passed</t>
+          <t>文本补全_判断使用guided_json时返回文本格式正确</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断设置max_tokens，使用束搜索</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>passed</t>
+          <t>文本补全_判断温度不同返回结果改变</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断设置max_tokens，返回结果正确</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+          <t>文本补全_判断目前不支持guided_choice</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -915,10 +921,10 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>文本补全_判断设置stop字符串时，输出结果正确</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+          <t>文本补全_判断目前不支持guided_regex</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -927,10 +933,58 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>文本补全_判断设置max_tokens，使用束搜索</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>文本补全_判断设置max_tokens，返回结果正确</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>文本补全_判断设置stop字符串时，输出结果正确</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>文本补全_判断非stream模式下，使用stream_options报400（4个组合）</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>文本补全_判断非stream模式输出结果正确</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
